--- a/BenchmarkSimScore.xlsx
+++ b/BenchmarkSimScore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/pb669_drexel_edu/Documents/PhD/Articles/Journal - Kris/GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_975EF0DBD03D6D55043D3B353F7312568254C302" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5638AA43-D6D1-4C1C-B7D1-3D44760C1553}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_975EF0DBD03D6D55043D3B353F7312568254C302" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14EA018F-F5E4-414F-A203-7714D262664C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BenchMark" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Sentence1</t>
   </si>
@@ -76,40 +76,85 @@
     <t>Model 16</t>
   </si>
   <si>
-    <t>The concrete bridge is under construction by the men in the working area</t>
-  </si>
-  <si>
-    <t>There are men working to build the bridge out of concrete</t>
-  </si>
-  <si>
-    <t>The concrete foundation of the skyscraper is stiff enough to withstand the earthquake load</t>
-  </si>
-  <si>
-    <t>The building foundation can resist the seismic load due to the high stiffness of the concrete material</t>
-  </si>
-  <si>
-    <t>The abandoned wooden house is demolished due to rotting issue</t>
-  </si>
-  <si>
-    <t>The site workers deconstructed the left-alone rotted wooden house</t>
-  </si>
-  <si>
-    <t>The rusting issue is detectable in the steel beam</t>
-  </si>
-  <si>
-    <t>The wooden deck of the sidewalk is architecturally appealing</t>
-  </si>
-  <si>
-    <t>The bridge deck includes concrete and asphalt</t>
-  </si>
-  <si>
-    <t>The column of the theater needs to be repaired</t>
-  </si>
-  <si>
-    <t>The concrete pier has widespread alkali-silica reaction cracks</t>
-  </si>
-  <si>
-    <t>A building deconstruction is happening to rebuild a new one</t>
+    <t>The concrete bridge is under construction by the men in the working area.</t>
+  </si>
+  <si>
+    <t>There are men working to build the bridge out of concrete.</t>
+  </si>
+  <si>
+    <t>The concrete foundation of the skyscraper is stiff enough to withstand the earthquake load.</t>
+  </si>
+  <si>
+    <t>The building foundation can resist the seismic load due to the high stiffness of the concrete material.</t>
+  </si>
+  <si>
+    <t>The abandoned wooden house is demolished due to rotting issue.</t>
+  </si>
+  <si>
+    <t>The site workers deconstructed the left-alone rotted wooden house.</t>
+  </si>
+  <si>
+    <t>The steel reinforcement bars are being placed for the concrete slab.</t>
+  </si>
+  <si>
+    <t>Workers are arranging rebar in preparation for pouring concrete.</t>
+  </si>
+  <si>
+    <t>The construction site has scaffolding erected around the building.</t>
+  </si>
+  <si>
+    <t>Temporary scaffolding is installed to allow workers to access upper floors.</t>
+  </si>
+  <si>
+    <t>The timber beams are cut to fit the roof structure of the building.</t>
+  </si>
+  <si>
+    <t>Wooden planks are trimmed and aligned to form the roof framework.</t>
+  </si>
+  <si>
+    <t>The rusting issue is detectable in the steel beam.</t>
+  </si>
+  <si>
+    <t>The wooden deck of the sidewalk is architecturally appealing.</t>
+  </si>
+  <si>
+    <t>The bridge deck includes concrete and asphalt.</t>
+  </si>
+  <si>
+    <t>The column of the theater needs to be repaired.</t>
+  </si>
+  <si>
+    <t>The concrete pier has widespread alkali-silica reaction cracks.</t>
+  </si>
+  <si>
+    <t>A building deconstruction is happening to rebuild a new one.</t>
+  </si>
+  <si>
+    <t>The damaged asphalt pavement requires immediate maintenance.</t>
+  </si>
+  <si>
+    <t>A steel column in the high-rise building needs to be painted.</t>
+  </si>
+  <si>
+    <t>The site worker is measuring the distance using a laser tool.</t>
+  </si>
+  <si>
+    <t>The concrete mixture is being transported in a cement truck.</t>
+  </si>
+  <si>
+    <t>The glass panels are being installed on the building facade.</t>
+  </si>
+  <si>
+    <t>The excavator is digging trenches for underground utility lines.</t>
+  </si>
+  <si>
+    <t>Model 17</t>
+  </si>
+  <si>
+    <t>Model 18</t>
+  </si>
+  <si>
+    <t>Model 19</t>
   </si>
 </sst>
 </file>
@@ -137,10 +182,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -163,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -172,7 +217,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,16 +531,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.9296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -551,422 +595,803 @@
       <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="T1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2">
-        <v>0.84840953350067139</v>
+        <v>0.85303807258605957</v>
       </c>
       <c r="E2" s="2">
-        <v>0.9390978217124939</v>
+        <v>0.94528031349182129</v>
       </c>
       <c r="F2" s="2">
-        <v>0.86243569850921631</v>
+        <v>0.85478699207305908</v>
       </c>
       <c r="G2" s="2">
-        <v>0.89807003736495972</v>
+        <v>0.8772352933883667</v>
       </c>
       <c r="H2" s="2">
-        <v>0.90544635057449341</v>
+        <v>0.90696442127227783</v>
       </c>
       <c r="I2" s="2">
-        <v>0.90605050325393677</v>
+        <v>0.9049716591835022</v>
       </c>
       <c r="J2" s="2">
-        <v>0.86916673183441162</v>
+        <v>0.86214905977249146</v>
       </c>
       <c r="K2" s="2">
-        <v>0.90060657262802124</v>
+        <v>0.91054195165634155</v>
       </c>
       <c r="L2" s="2">
-        <v>0.88983362913131714</v>
+        <v>0.84788107872009277</v>
       </c>
       <c r="M2" s="2">
-        <v>0.93045216798782349</v>
+        <v>0.93375265598297119</v>
       </c>
       <c r="N2" s="2">
-        <v>0.923228919506073</v>
+        <v>0.91420942544937134</v>
       </c>
       <c r="O2" s="2">
-        <v>0.93342477083206177</v>
+        <v>0.93897992372512817</v>
       </c>
       <c r="P2" s="2">
-        <v>0.87496310472488403</v>
+        <v>0.87413632869720459</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.84568643569946289</v>
+        <v>0.82629835605621338</v>
       </c>
       <c r="R2" s="2">
-        <v>0.86696285009384155</v>
+        <v>0.84267270565032959</v>
       </c>
       <c r="S2" s="2">
-        <v>0.27777777777777779</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+        <v>2.2226499462345551E-2</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.1953125</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.2105263157894737</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2">
-        <v>0.79378920793533325</v>
+        <v>0.80415254831314087</v>
       </c>
       <c r="E3" s="2">
-        <v>0.89267462491989136</v>
+        <v>0.89486277103424072</v>
       </c>
       <c r="F3" s="2">
-        <v>0.91432559490203857</v>
+        <v>0.90563666820526123</v>
       </c>
       <c r="G3" s="2">
-        <v>0.8330501914024353</v>
+        <v>0.83038824796676636</v>
       </c>
       <c r="H3" s="2">
-        <v>0.79853284358978271</v>
+        <v>0.72785735130310059</v>
       </c>
       <c r="I3" s="2">
-        <v>0.87924003601074219</v>
+        <v>0.8376128077507019</v>
       </c>
       <c r="J3" s="2">
-        <v>0.83627331256866455</v>
+        <v>0.80527669191360474</v>
       </c>
       <c r="K3" s="2">
-        <v>0.85103058815002441</v>
+        <v>0.82120072841644287</v>
       </c>
       <c r="L3" s="2">
-        <v>0.87230515480041504</v>
+        <v>0.82895970344543457</v>
       </c>
       <c r="M3" s="2">
-        <v>0.89871752262115479</v>
+        <v>0.89832550287246704</v>
       </c>
       <c r="N3" s="2">
-        <v>0.80302077531814575</v>
+        <v>0.70757365226745605</v>
       </c>
       <c r="O3" s="2">
-        <v>0.87421870231628418</v>
+        <v>0.848288893699646</v>
       </c>
       <c r="P3" s="2">
-        <v>0.84024232625961304</v>
+        <v>0.83277183771133423</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.75114870071411133</v>
+        <v>0.73288160562515259</v>
       </c>
       <c r="R3" s="2">
-        <v>0.81908708810806274</v>
+        <v>0.7999873161315918</v>
       </c>
       <c r="S3" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+        <v>3.3271889139709507E-2</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0.32258064516129031</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0.31468531468531458</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2">
-        <v>0.72515887022018433</v>
+        <v>0.69744086265563965</v>
       </c>
       <c r="E4" s="2">
-        <v>0.83612954616546631</v>
+        <v>0.83635371923446655</v>
       </c>
       <c r="F4" s="2">
-        <v>0.76917684078216553</v>
+        <v>0.72151559591293335</v>
       </c>
       <c r="G4" s="2">
-        <v>0.72067683935165405</v>
+        <v>0.71341902017593384</v>
       </c>
       <c r="H4" s="2">
-        <v>0.71102231740951538</v>
+        <v>0.69732439517974854</v>
       </c>
       <c r="I4" s="2">
-        <v>0.72318184375762939</v>
+        <v>0.67635166645050049</v>
       </c>
       <c r="J4" s="2">
-        <v>0.6582646369934082</v>
+        <v>0.63180536031723022</v>
       </c>
       <c r="K4" s="2">
-        <v>0.68501847982406616</v>
+        <v>0.65546822547912598</v>
       </c>
       <c r="L4" s="2">
-        <v>0.77266466617584229</v>
+        <v>0.74038034677505493</v>
       </c>
       <c r="M4" s="2">
-        <v>0.76778852939605713</v>
+        <v>0.76557695865631104</v>
       </c>
       <c r="N4" s="2">
-        <v>0.67000597715377808</v>
+        <v>0.59355992078781128</v>
       </c>
       <c r="O4" s="2">
-        <v>0.75980204343795776</v>
+        <v>0.77571582794189453</v>
       </c>
       <c r="P4" s="2">
-        <v>0.62043839693069458</v>
+        <v>0.6163182258605957</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.66611945629119873</v>
+        <v>0.63025939464569092</v>
       </c>
       <c r="R4" s="2">
-        <v>0.67844855785369873</v>
+        <v>0.65080714225769043</v>
       </c>
       <c r="S4" s="2">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+        <v>2.5518615589394281E-2</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.15151515151515149</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0.1176470588235294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2">
-        <v>0.17795354127883911</v>
+        <v>0.64346194267272949</v>
       </c>
       <c r="E5" s="2">
-        <v>0.4224521815776825</v>
+        <v>0.76458543539047241</v>
       </c>
       <c r="F5" s="2">
-        <v>0.67157697677612305</v>
+        <v>0.75772523880004883</v>
       </c>
       <c r="G5" s="2">
-        <v>0.29552698135375982</v>
+        <v>0.70463937520980835</v>
       </c>
       <c r="H5" s="2">
-        <v>0.2263337969779968</v>
+        <v>0.62143778800964355</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6765803396701813E-2</v>
+        <v>0.54866313934326172</v>
       </c>
       <c r="J5" s="2">
-        <v>0.15141759812831879</v>
+        <v>0.59460318088531494</v>
       </c>
       <c r="K5" s="2">
-        <v>-5.5757943540811539E-2</v>
+        <v>0.54947441816329956</v>
       </c>
       <c r="L5" s="2">
-        <v>0.16307662427425379</v>
+        <v>0.5934109091758728</v>
       </c>
       <c r="M5" s="2">
-        <v>0.27998775243759161</v>
+        <v>0.64687246084213257</v>
       </c>
       <c r="N5" s="2">
-        <v>0.26871797442436218</v>
+        <v>0.57083457708358765</v>
       </c>
       <c r="O5" s="2">
-        <v>0.22008596360683441</v>
+        <v>0.67993438243865967</v>
       </c>
       <c r="P5" s="2">
-        <v>0.26232615113258362</v>
+        <v>0.59503817558288574</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.15322355926036829</v>
+        <v>0.59110510349273682</v>
       </c>
       <c r="R5" s="2">
-        <v>0.11015138030052191</v>
+        <v>0.6247069239616394</v>
       </c>
       <c r="S5" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+        <v>2.283506054006211E-2</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="U5" s="1">
+        <v>9.2592592592592587E-2</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2">
-        <v>0.25895145535469061</v>
+        <v>0.67100203037261963</v>
       </c>
       <c r="E6" s="2">
-        <v>0.36685514450073242</v>
+        <v>0.73628944158554077</v>
       </c>
       <c r="F6" s="2">
-        <v>0.52009421586990356</v>
+        <v>0.79747265577316284</v>
       </c>
       <c r="G6" s="2">
-        <v>0.29964748024940491</v>
+        <v>0.75166040658950806</v>
       </c>
       <c r="H6" s="2">
-        <v>0.14141033589839941</v>
+        <v>0.66768991947174072</v>
       </c>
       <c r="I6" s="2">
-        <v>0.132862314581871</v>
+        <v>0.67688161134719849</v>
       </c>
       <c r="J6" s="2">
-        <v>0.11506087332963939</v>
+        <v>0.75692129135131836</v>
       </c>
       <c r="K6" s="2">
-        <v>5.5463291704654687E-2</v>
+        <v>0.69223791360855103</v>
       </c>
       <c r="L6" s="2">
-        <v>0.1108582094311714</v>
+        <v>0.63312089443206787</v>
       </c>
       <c r="M6" s="2">
-        <v>0.3851439356803894</v>
+        <v>0.7150464653968811</v>
       </c>
       <c r="N6" s="2">
-        <v>0.32408452033996582</v>
+        <v>0.6374548077583313</v>
       </c>
       <c r="O6" s="2">
-        <v>0.25214302539825439</v>
+        <v>0.71980243921279907</v>
       </c>
       <c r="P6" s="2">
-        <v>0.30573827028274542</v>
+        <v>0.6444091796875</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.103256992995739</v>
+        <v>0.38232746720314031</v>
       </c>
       <c r="R6" s="2">
-        <v>0.10884272307157521</v>
+        <v>0.4139992892742157</v>
       </c>
       <c r="S6" s="2">
-        <v>6.6666666666666666E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+        <v>1.885031902274735E-2</v>
+      </c>
+      <c r="T6" s="1">
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="U6" s="1">
+        <v>5.4347826086956513E-2</v>
+      </c>
+      <c r="V6" s="1">
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="2">
-        <v>0.30028730630874628</v>
+        <v>0.76304787397384644</v>
       </c>
       <c r="E7" s="2">
-        <v>0.39792007207870478</v>
+        <v>0.85234463214874268</v>
       </c>
       <c r="F7" s="2">
-        <v>0.59545153379440308</v>
+        <v>0.82772558927536011</v>
       </c>
       <c r="G7" s="2">
-        <v>0.42974582314491272</v>
+        <v>0.74606049060821533</v>
       </c>
       <c r="H7" s="2">
-        <v>0.26797997951507568</v>
+        <v>0.73247355222702026</v>
       </c>
       <c r="I7" s="2">
-        <v>0.22614336013793951</v>
+        <v>0.67257416248321533</v>
       </c>
       <c r="J7" s="2">
-        <v>0.23379579186439511</v>
+        <v>0.64971035718917847</v>
       </c>
       <c r="K7" s="2">
-        <v>0.22399555146694181</v>
+        <v>0.67733246088027954</v>
       </c>
       <c r="L7" s="2">
-        <v>0.24611373245716089</v>
+        <v>0.64053463935852051</v>
       </c>
       <c r="M7" s="2">
-        <v>0.37746515870094299</v>
+        <v>0.83458411693572998</v>
       </c>
       <c r="N7" s="2">
-        <v>0.31786543130874628</v>
+        <v>0.70137166976928711</v>
       </c>
       <c r="O7" s="2">
-        <v>0.36515957117080688</v>
+        <v>0.78498625755310059</v>
       </c>
       <c r="P7" s="2">
-        <v>0.24282737076282501</v>
+        <v>0.726726233959198</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.21530567109584811</v>
+        <v>0.73449259996414185</v>
       </c>
       <c r="R7" s="2">
-        <v>0.18339286744594571</v>
+        <v>0.75688660144805908</v>
       </c>
       <c r="S7" s="2">
+        <v>3.9524926351130293E-2</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.33333333333333343</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0.29062500000000002</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.2105263157894737</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.18718761205673221</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.43199244141578669</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.63188844919204712</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.30586054921150208</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.2150065004825592</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.7464111149311066E-2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.17364555597305301</v>
+      </c>
+      <c r="K8" s="2">
+        <v>-2.2740093991160389E-2</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.10111527889966961</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.30028554797172552</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.27753117680549622</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.20381179451942441</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.26236692070960999</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.13894976675510409</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.10768921673297881</v>
+      </c>
+      <c r="S8" s="2">
+        <v>3.1559845391129458E-2</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.21266390383243561</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.39122453331947332</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.5408705472946167</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.2970554530620575</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1142008379101753</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.1088983863592148</v>
+      </c>
+      <c r="J9" s="2">
+        <v>8.3079271018505096E-2</v>
+      </c>
+      <c r="K9" s="2">
+        <v>3.3965412527322769E-2</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.1043084189295769</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.37282267212867742</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.23196615278720861</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.22405423223972321</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.30285835266113281</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>8.1327624619007111E-2</v>
+      </c>
+      <c r="R9" s="2">
+        <v>9.5563650131225586E-2</v>
+      </c>
+      <c r="S9" s="2">
+        <v>2.398029676182711E-2</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.125</v>
+      </c>
+      <c r="U9" s="1">
+        <v>6.9444444444444448E-2</v>
+      </c>
+      <c r="V9" s="1">
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.31344550848007202</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.42817583680152888</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.60045677423477173</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.5363801121711731</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.2579156756401062</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.20210082828998571</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.26994678378105158</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.2219642847776413</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.27775135636329651</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.35515552759170532</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.27698025107383728</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.32760739326477051</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.23765017092227941</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.18451219797134399</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.16411082446575159</v>
+      </c>
+      <c r="S10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.23766650259494779</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.59810775518417358</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.69601535797119141</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.56388550996780396</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.2423407435417175</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.5780625939369202E-2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.25567194819450378</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.17991520464420321</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.21158008277416229</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.33353325724601751</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.15890379250049591</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.26006841659545898</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.18467280268669131</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.27421054244041437</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0.26549163460731512</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.10526315789473691</v>
+      </c>
+      <c r="U11" s="1">
+        <v>6.7567567567567571E-2</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.1252661049365997</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.29553765058517462</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.73219746351242065</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.50033420324325562</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.15230794250965121</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.14988735318183899</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.24206642806529999</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.11130896955728529</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.1651372313499451</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.24791271984577179</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.29530003666877752</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.121479444205761</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.2014729380607605</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>2.485816553235054E-2</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1.8610607832670208E-2</v>
+      </c>
+      <c r="S12" s="2">
+        <v>2.5132936350227661E-2</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.28571428571428559</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0.13761467889908249</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.12343466281890871</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.19852091372013089</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.7082982063293457</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.3813997209072113</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1.5549094416201109E-2</v>
+      </c>
+      <c r="I13" s="2">
+        <v>2.6286264881491661E-2</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.14032886922359469</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.15814791619777679</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.17093111574649811</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.17428396642208099</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0.131496787071228</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.14639826118946081</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.17533992230892179</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0.25094586610794067</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0.2184451222419739</v>
+      </c>
+      <c r="S13" s="2">
+        <v>2.145851237135921E-2</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0.10526315789473691</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0.10101010101010099</v>
+      </c>
+      <c r="V13" s="1">
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -984,58 +1409,59 @@
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N17" s="1"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N18" s="1"/>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N19" s="1"/>
       <c r="O19" s="3"/>
     </row>
-    <row r="20" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N20" s="1"/>
       <c r="O20" s="3"/>
     </row>
-    <row r="21" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N21" s="1"/>
       <c r="O21" s="3"/>
     </row>
-    <row r="22" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N22" s="1"/>
       <c r="O22" s="3"/>
     </row>
-    <row r="23" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N23" s="1"/>
       <c r="O23" s="3"/>
     </row>
-    <row r="24" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N24" s="1"/>
       <c r="O24" s="3"/>
     </row>
-    <row r="25" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N25" s="1"/>
       <c r="O25" s="3"/>
     </row>
-    <row r="26" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="14:15" x14ac:dyDescent="0.45">
       <c r="N28" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>